--- a/Employee_Reports_wi52/Arjay Imperial Gabarda Q0620.xlsx
+++ b/Employee_Reports_wi52/Arjay Imperial Gabarda Q0620.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1207,11 +1207,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1305,11 +1305,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1354,11 +1354,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1403,11 +1403,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1440,11 +1440,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1477,11 +1477,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7907</v>
+        <v>7899</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7895</v>
+        <v>7887</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7895</v>
+        <v>7887</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
